--- a/data-manipulation-scripts/sheets-cleanup/sheets/EIXO SELETOR.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/EIXO SELETOR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -81,6 +81,42 @@
   <si>
     <t>EIXO SELETOR CAMBIO SMARTFOX BIZ100</t>
   </si>
+  <si>
+    <t>7899468089503</t>
+  </si>
+  <si>
+    <t>EIXO SELETOR CAMBIO MHX POP110I 2016 A 2021</t>
+  </si>
+  <si>
+    <t>7899468089510</t>
+  </si>
+  <si>
+    <t>EIXO SELETOR CAMBIO MHX POP100 2007 A 2015</t>
+  </si>
+  <si>
+    <t>7908305601645</t>
+  </si>
+  <si>
+    <t>EIXO SELETOR CAMBIO MHX TWISTER250/ TORNADO250/ XRE300/ CB300R</t>
+  </si>
+  <si>
+    <t>751320984449</t>
+  </si>
+  <si>
+    <t>EIXO SELETOR CAMBIO IRON  YBR125 2008/ XTZ125/ FACTOR125 182719</t>
+  </si>
+  <si>
+    <t>751320984425</t>
+  </si>
+  <si>
+    <t>EIXO SELETOR CAMBIO IRON TITAN150/ FAN125 2009</t>
+  </si>
+  <si>
+    <t>751320984500</t>
+  </si>
+  <si>
+    <t>EIXO CAMBIO IRON FAZER250 2018/ XTZ250 LANDER</t>
+  </si>
 </sst>
 </file>
 
@@ -143,7 +179,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -449,7 +485,9 @@
       <c r="C3" s="4">
         <v>1.0</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6">
+        <v>60.0</v>
+      </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -483,7 +521,9 @@
       <c r="C4" s="4">
         <v>1.0</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="6">
+        <v>75.0</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -553,7 +593,9 @@
       <c r="C6" s="7">
         <v>2.0</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="6">
+        <v>80.0</v>
+      </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -587,7 +629,9 @@
       <c r="C7" s="7">
         <v>8.0</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="6">
+        <v>75.0</v>
+      </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -720,46 +764,220 @@
       <c r="Z10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>65.0</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="7">
+        <v>65.0</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>75.0</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="6">
+        <v>78.0</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="7">
+        <v>78.0</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
     </row>
     <row r="16">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>78.0</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="8"/>
